--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -16,9 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
-    <t>退款单号</t>
-  </si>
-  <si>
     <t>订单号</t>
   </si>
   <si>
@@ -35,6 +32,9 @@
   </si>
   <si>
     <t>汇率</t>
+  </si>
+  <si>
+    <t>结算汇率</t>
   </si>
   <si>
     <t>下单人</t>
@@ -715,11 +715,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1041,8 +1044,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="15" max="15" width="9.375"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:19">
       <c r="A1" s="1" t="s">
@@ -1103,7 +1109,28 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="15:15">
+      <c r="O2" s="2"/>
+    </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+25</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -14,21 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>订单号</t>
-  </si>
-  <si>
-    <t>平台名称</t>
-  </si>
-  <si>
-    <t>站点</t>
-  </si>
-  <si>
-    <t>店铺名称</t>
-  </si>
-  <si>
-    <t>订单销售额[原币种]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>*订单号</t>
+  </si>
+  <si>
+    <t>*平台名称</t>
+  </si>
+  <si>
+    <t>*站点</t>
+  </si>
+  <si>
+    <t>*店铺名称</t>
+  </si>
+  <si>
+    <t>*订单销售额[原币种]</t>
   </si>
   <si>
     <t>汇率</t>
@@ -37,7 +37,7 @@
     <t>结算汇率</t>
   </si>
   <si>
-    <t>下单人</t>
+    <t>*下单人</t>
   </si>
   <si>
     <t>下单电话1</t>
@@ -52,10 +52,10 @@
     <t>下单地址2</t>
   </si>
   <si>
-    <t>国家名称</t>
-  </si>
-  <si>
-    <t>订单状态</t>
+    <t>*国家名称</t>
+  </si>
+  <si>
+    <t>*订单状态</t>
   </si>
   <si>
     <t>订单下单时间</t>
@@ -64,10 +64,22 @@
     <t>订单发货时间</t>
   </si>
   <si>
-    <t>销售员</t>
+    <t>*销售员</t>
   </si>
   <si>
     <t>币种</t>
+  </si>
+  <si>
+    <t>*SKU</t>
+  </si>
+  <si>
+    <t>*品名</t>
+  </si>
+  <si>
+    <t>*单价</t>
+  </si>
+  <si>
+    <t>*数量</t>
   </si>
   <si>
     <t>错误信息</t>
@@ -715,7 +727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -723,6 +735,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1044,13 +1059,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="15" max="15" width="9.375"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:19">
+    <row r="1" customFormat="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1107,20 +1122,28 @@
       </c>
       <c r="S1" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="15:15">
       <c r="O2" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+25</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>0</formula1>
@@ -1130,6 +1153,18 @@
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>*订单号</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>*数量</t>
-  </si>
-  <si>
-    <t>错误信息</t>
   </si>
 </sst>
 </file>
@@ -1059,13 +1056,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:23">
+    <row r="1" customFormat="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,9 +1128,6 @@
       </c>
       <c r="V1" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="15:15">
@@ -1144,6 +1138,10 @@
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+25</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>0</formula1>
@@ -1157,10 +1155,6 @@
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990</formula2>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -58,7 +58,7 @@
     <t>*订单状态</t>
   </si>
   <si>
-    <t>订单下单时间</t>
+    <t>*订单下单时间</t>
   </si>
   <si>
     <t>订单发货时间</t>
@@ -1134,7 +1134,7 @@
       <c r="O2" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+25</formula2>
@@ -1155,6 +1155,9 @@
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+      <formula1>"配货中,已发货,已完成,已作废"</formula1>
+    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990</formula2>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>*订单号</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>*销售员</t>
+  </si>
+  <si>
+    <t>*销售事业部</t>
   </si>
   <si>
     <t>币种</t>
@@ -1056,13 +1059,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:22">
+    <row r="1" customFormat="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1123,7 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="3" t="s">
@@ -1128,6 +1131,9 @@
       </c>
       <c r="V1" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="15:15">
@@ -1139,7 +1145,7 @@
       <formula1>0</formula1>
       <formula2>9.99999999999999E+25</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
     </dataValidation>
@@ -1151,14 +1157,14 @@
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+      <formula1>"配货中,已发货,已完成,已作废"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576 R2:R1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
-      <formula1>"配货中,已发货,已完成,已作废"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
       <formula1>0</formula1>
       <formula2>9999999999999990</formula2>
     </dataValidation>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -1160,7 +1160,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>"配货中,已发货,已完成,已作废"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576 R2:R1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -1158,7 +1158,7 @@
       <formula2>99999999999999900000</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
-      <formula1>"配货中,已发货,已完成,已作废"</formula1>
+      <formula1>"配货中,已发货,已完成,已作废,退货,退款"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 P2:P1048576">
       <formula1>25569</formula1>

--- a/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/dmpOrderInfoTemplate.xlsx
@@ -1062,7 +1062,7 @@
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:23">
@@ -1157,6 +1157,10 @@
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999990</formula2>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>"配货中,已发货,已完成,已作废,退货,退款"</formula1>
     </dataValidation>
@@ -1164,10 +1168,6 @@
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999990</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
